--- a/forms/trg/Formulir_TRG_pmn-rg.xlsx
+++ b/forms/trg/Formulir_TRG_pmn-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B35)</f>
+        <f>COUNTA(Anggota!B5:B36)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F35)</f>
+        <f>COUNTA(Anggota!F5:F36)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,19 +913,15 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Elly L Sjattar, S.Kp., M.Kes</t>
+          <t>Dr. Yuliana Syam, S.Kep., Ns., M.Kes</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Faculty of Nursing Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
@@ -933,17 +929,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7376-5771</t>
+          <t>0000-0001-5078-4462</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>5989587</t>
+          <t>6033462</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57212209382</t>
+          <t>57193342137</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Aulia Insani Latif, S.Kep., Ns., M.Kep</t>
+          <t>Prof. Elly L Sjattar, S.Kp., M.Kes</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -978,17 +974,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-3987-3736</t>
+          <t>0000-0002-7376-5771</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6727541</t>
+          <t>5989587</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57214451599</t>
+          <t>57212209382</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Arnis Puspita Rasyid, S.Kep., Ns., M.Kes</t>
+          <t>Aulia Insani Latif, S.Kep., Ns., M.Kep</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1023,17 +1019,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0218-3499</t>
+          <t>0000-0002-3987-3736</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>https://sinta.kemdikbud.go.id/authors/scopusanalysis/6033431</t>
+          <t>6727541</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57215875636</t>
+          <t>57214451599</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,17 +1044,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Yuyun Widaningsih</t>
+          <t>Arnis Puspita Rasyid, S.Kep., Ns., M.Kes</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Medicine Hasanuddin University</t>
+          <t>Faculty of Nursing Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="n"/>
@@ -1068,17 +1064,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0009-0008-9058-4244</t>
+          <t>0000-0003-0218-3499</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6690255</t>
+          <t>https://sinta.kemdikbud.go.id/authors/scopusanalysis/6033431</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57207822408</t>
+          <t>57215875636</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1093,17 +1089,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Yusfina, S.Ft., Physio., M.Kes</t>
+          <t>Yuyun Widaningsih</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Faculty of Medicine Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="n"/>
@@ -1113,15 +1109,19 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7398-7278</t>
+          <t>0009-0008-9058-4244</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>6907379</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="n"/>
+          <t>6690255</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>57207822408</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Syahrul, S.Kep,. Ns., M.Kes., Ph.D</t>
+          <t>Yusfina, S.Ft., Physio., M.Kes</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Nursing Hasanuddin University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1154,19 +1154,15 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2939-4173</t>
+          <t>0000-0002-7398-7278</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>5976510</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>57188828353</t>
-        </is>
-      </c>
+          <t>6907379</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1179,12 +1175,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Riskah Nur`amalia, S.Ft., Physio., M.Biomed., Ph.D</t>
+          <t>Syahrul, S.Kep,. Ns., M.Kes., Ph.D</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1199,17 +1195,17 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5356-4166</t>
+          <t>0000-0003-2939-4173</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>6746377</t>
+          <t>5976510</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57220210839</t>
+          <t>57188828353</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1224,17 +1220,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nor Aziyan Binti Yahaya</t>
+          <t>Riskah Nur`amalia, S.Ft., Physio., M.Biomed., Ph.D</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>University of Malaya</t>
+          <t>Faculty of Nursing Hasanuddin University</t>
         </is>
       </c>
       <c r="E12" s="11" t="n"/>
@@ -1244,13 +1240,17 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-4225-2148</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="n"/>
+          <t>0000-0001-5356-4166</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>6746377</t>
+        </is>
+      </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>56567825500</t>
+          <t>57220210839</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Toshiaki Takahashi, PhD, RN</t>
+          <t>Dr. Nor Aziyan Binti Yahaya</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>School of Medicin : Nursing Course Yokohama City University</t>
+          <t>University of Malaya</t>
         </is>
       </c>
       <c r="E13" s="11" t="n"/>
@@ -1285,11 +1285,15 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-8188-2505</t>
+          <t>0000-0002-4225-2148</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>56567825500</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1302,17 +1306,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Petra Mandysová, RN, MSN, PhD</t>
+          <t>Toshiaki Takahashi, PhD, RN</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>University of Pardubice, Faculty of Health Studies</t>
+          <t>School of Medicin : Nursing Course Yokohama City University</t>
         </is>
       </c>
       <c r="E14" s="11" t="n"/>
@@ -1322,15 +1326,11 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7399-1456</t>
+          <t>0000-0002-8188-2505</t>
         </is>
       </c>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>23969350300</t>
-        </is>
-      </c>
+      <c r="L14" s="12" t="n"/>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1343,17 +1343,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Prof. Chrysoula Tsiou</t>
+          <t>Assoc. Prof. Petra Mandysová, RN, MSN, PhD</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>University of West Attica, Greece</t>
+          <t>University of Pardubice, Faculty of Health Studies</t>
         </is>
       </c>
       <c r="E15" s="11" t="n"/>
@@ -1363,13 +1363,13 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1243-7069</t>
+          <t>0000-0001-7399-1456</t>
         </is>
       </c>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>23020314900</t>
+          <t>23969350300</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -1384,31 +1384,35 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Ns. Indra Atsah, S.Kep.,M.Kep</t>
+          <t>Prof. Chrysoula Tsiou</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>Sandi Karsa Hospital, Makassar</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>University of West Attica, Greece</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="n"/>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>0009-0004-6800-2931</t>
+          <t>0000-0003-1243-7069</t>
         </is>
       </c>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>23020314900</t>
+        </is>
+      </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1421,18 +1425,18 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Marce Marghareta Takumansang</t>
+          <t>Ns. Indra Atsah, S.Kep.,M.Kep</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Ampana Regional General Hospital, Tojo Una-Una Regency</t>
+          <t>Sandi Karsa Hospital, Makassar</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1441,7 +1445,7 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>0009-0002-7621-6820</t>
+          <t>0009-0004-6800-2931</t>
         </is>
       </c>
       <c r="K17" s="12" t="n"/>
@@ -1458,18 +1462,18 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Kiki Fatmawati M</t>
+          <t>Marce Marghareta Takumansang</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Sandi Karsa Hospital, Makassar</t>
+          <t>Ampana Regional General Hospital, Tojo Una-Una Regency</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1478,7 +1482,7 @@
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>0009-0008-9339-8842</t>
+          <t>0009-0002-7621-6820</t>
         </is>
       </c>
       <c r="K18" s="12" t="n"/>
@@ -1495,25 +1499,29 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Ulfatun Fahmiatun</t>
+          <t>Kiki Fatmawati M</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Faculty of Nursing Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Sandi Karsa Hospital, Makassar</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>0009-0008-9339-8842</t>
+        </is>
+      </c>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="11" t="inlineStr">
@@ -1528,12 +1536,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Darmawati</t>
+          <t>Ulfatun Fahmiatun</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1546,11 +1554,7 @@
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n"/>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>0009-0009-3889-1818</t>
-        </is>
-      </c>
+      <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="11" t="inlineStr">
@@ -1565,12 +1569,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Herlina</t>
+          <t>Darmawati</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1583,7 +1587,11 @@
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>0009-0009-3889-1818</t>
+        </is>
+      </c>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="11" t="inlineStr">
@@ -1598,12 +1606,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Widyastuti</t>
+          <t>Herlina</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1616,11 +1624,7 @@
       <c r="G22" s="12" t="n"/>
       <c r="H22" s="12" t="n"/>
       <c r="I22" s="12" t="n"/>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>0009-0007-9048-2929</t>
-        </is>
-      </c>
+      <c r="J22" s="12" t="n"/>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="11" t="inlineStr">
@@ -1635,12 +1639,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Farawansah</t>
+          <t>Widyastuti</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1655,7 +1659,7 @@
       <c r="I23" s="12" t="n"/>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>0009-0003-9909-6208</t>
+          <t>0009-0007-9048-2929</t>
         </is>
       </c>
       <c r="K23" s="12" t="n"/>
@@ -1670,18 +1674,42 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="11" t="n"/>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Farawansah</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Faculty of Nursing Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>The Pain Management Nursing Research Group is dedicated to advancing nursing science and practice in the field of pain management across diverse populations and healthcare settings. Pain is a complex, multidimensional experience that affects individuals physically, psychologically, socially, and spiritually. Consequently, effective pain management is a fundamental component of quality nursing care and patient safety.</t>
+        </is>
+      </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>0009-0003-9909-6208</t>
+        </is>
+      </c>
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1870,15 +1898,32 @@
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
